--- a/Abaqus_files/Abaqus_to_Excel.xlsx
+++ b/Abaqus_files/Abaqus_to_Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\st195764\Desktop\Spiral-Simulation\Abaqus_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A543C2-0773-4FD2-B116-0CF3F00AAE4A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7040C935-8048-478D-B499-30B465765423}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
